--- a/1. Reporting_Data/IB_Daily Ticker/processed/2025/202510/Ticker_20251023.xlsx
+++ b/1. Reporting_Data/IB_Daily Ticker/processed/2025/202510/Ticker_20251023.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="357">
   <si>
     <t>Symbol</t>
   </si>
@@ -556,9 +556,6 @@
     <t>OPT</t>
   </si>
   <si>
-    <t>WAR</t>
-  </si>
-  <si>
     <t>FOP</t>
   </si>
   <si>
@@ -601,9 +598,6 @@
     <t>Bond</t>
   </si>
   <si>
-    <t>Other</t>
-  </si>
-  <si>
     <t>1109 HK Equity</t>
   </si>
   <si>
@@ -758,6 +752,9 @@
   </si>
   <si>
     <t>DFDV US Equity</t>
+  </si>
+  <si>
+    <t>DFDVW US Equity</t>
   </si>
   <si>
     <t>DG US Equity</t>
@@ -1479,13 +1476,13 @@
         <v>178</v>
       </c>
       <c r="D2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1499,13 +1496,13 @@
         <v>178</v>
       </c>
       <c r="D3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1519,13 +1516,13 @@
         <v>178</v>
       </c>
       <c r="D4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F4" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1539,13 +1536,13 @@
         <v>178</v>
       </c>
       <c r="D5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1559,13 +1556,13 @@
         <v>178</v>
       </c>
       <c r="D6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F6" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1579,13 +1576,13 @@
         <v>178</v>
       </c>
       <c r="D7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F7" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1599,13 +1596,13 @@
         <v>178</v>
       </c>
       <c r="D8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F8" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1619,13 +1616,13 @@
         <v>178</v>
       </c>
       <c r="D9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F9" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1639,13 +1636,13 @@
         <v>178</v>
       </c>
       <c r="D10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F10" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1659,13 +1656,13 @@
         <v>178</v>
       </c>
       <c r="D11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E11" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F11" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1679,13 +1676,13 @@
         <v>178</v>
       </c>
       <c r="D12" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F12" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1699,13 +1696,13 @@
         <v>178</v>
       </c>
       <c r="D13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F13" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1719,13 +1716,13 @@
         <v>179</v>
       </c>
       <c r="D14" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E14" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F14" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1739,13 +1736,13 @@
         <v>179</v>
       </c>
       <c r="D15" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E15" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F15" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1759,13 +1756,13 @@
         <v>179</v>
       </c>
       <c r="D16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E16" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F16" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1779,13 +1776,13 @@
         <v>179</v>
       </c>
       <c r="D17" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E17" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F17" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1799,13 +1796,13 @@
         <v>178</v>
       </c>
       <c r="D18" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E18" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F18" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1819,13 +1816,13 @@
         <v>178</v>
       </c>
       <c r="D19" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E19" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F19" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1839,13 +1836,13 @@
         <v>178</v>
       </c>
       <c r="D20" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E20" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F20" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1859,13 +1856,13 @@
         <v>178</v>
       </c>
       <c r="D21" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E21" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F21" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1879,13 +1876,13 @@
         <v>178</v>
       </c>
       <c r="D22" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E22" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F22" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1899,13 +1896,13 @@
         <v>178</v>
       </c>
       <c r="D23" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E23" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F23" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1919,13 +1916,13 @@
         <v>178</v>
       </c>
       <c r="D24" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E24" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F24" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -1939,13 +1936,13 @@
         <v>178</v>
       </c>
       <c r="D25" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E25" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F25" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1959,13 +1956,13 @@
         <v>178</v>
       </c>
       <c r="D26" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E26" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F26" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1979,13 +1976,13 @@
         <v>178</v>
       </c>
       <c r="D27" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E27" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F27" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -1999,13 +1996,13 @@
         <v>178</v>
       </c>
       <c r="D28" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E28" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F28" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -2019,13 +2016,13 @@
         <v>178</v>
       </c>
       <c r="D29" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E29" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F29" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -2039,13 +2036,13 @@
         <v>178</v>
       </c>
       <c r="D30" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E30" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F30" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -2059,13 +2056,13 @@
         <v>178</v>
       </c>
       <c r="D31" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E31" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F31" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -2079,13 +2076,13 @@
         <v>178</v>
       </c>
       <c r="D32" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E32" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F32" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -2099,13 +2096,13 @@
         <v>178</v>
       </c>
       <c r="D33" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F33" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -2119,13 +2116,13 @@
         <v>178</v>
       </c>
       <c r="D34" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E34" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F34" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -2139,13 +2136,13 @@
         <v>178</v>
       </c>
       <c r="D35" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E35" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F35" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -2159,13 +2156,13 @@
         <v>178</v>
       </c>
       <c r="D36" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E36" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F36" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -2179,13 +2176,13 @@
         <v>178</v>
       </c>
       <c r="D37" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E37" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F37" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -2199,13 +2196,13 @@
         <v>178</v>
       </c>
       <c r="D38" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E38" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F38" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -2219,13 +2216,13 @@
         <v>178</v>
       </c>
       <c r="D39" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E39" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F39" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -2239,13 +2236,13 @@
         <v>178</v>
       </c>
       <c r="D40" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E40" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F40" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -2259,13 +2256,13 @@
         <v>178</v>
       </c>
       <c r="D41" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E41" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F41" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -2279,13 +2276,13 @@
         <v>178</v>
       </c>
       <c r="D42" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E42" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F42" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -2299,13 +2296,13 @@
         <v>178</v>
       </c>
       <c r="D43" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E43" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F43" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -2319,13 +2316,13 @@
         <v>178</v>
       </c>
       <c r="D44" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E44" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F44" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -2339,13 +2336,13 @@
         <v>178</v>
       </c>
       <c r="D45" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E45" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F45" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -2359,13 +2356,13 @@
         <v>178</v>
       </c>
       <c r="D46" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E46" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F46" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -2379,13 +2376,13 @@
         <v>178</v>
       </c>
       <c r="D47" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E47" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F47" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -2399,13 +2396,13 @@
         <v>178</v>
       </c>
       <c r="D48" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E48" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F48" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -2419,13 +2416,13 @@
         <v>178</v>
       </c>
       <c r="D49" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E49" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F49" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -2439,13 +2436,13 @@
         <v>178</v>
       </c>
       <c r="D50" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E50" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F50" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -2459,13 +2456,13 @@
         <v>178</v>
       </c>
       <c r="D51" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E51" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F51" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -2479,13 +2476,13 @@
         <v>178</v>
       </c>
       <c r="D52" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E52" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F52" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -2499,13 +2496,13 @@
         <v>178</v>
       </c>
       <c r="D53" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E53" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F53" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -2516,13 +2513,16 @@
         <v>177</v>
       </c>
       <c r="C54" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D54" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E54" t="s">
-        <v>195</v>
+        <v>190</v>
+      </c>
+      <c r="F54" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -2536,13 +2536,13 @@
         <v>178</v>
       </c>
       <c r="D55" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E55" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F55" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -2556,13 +2556,13 @@
         <v>178</v>
       </c>
       <c r="D56" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E56" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F56" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -2576,13 +2576,13 @@
         <v>178</v>
       </c>
       <c r="D57" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E57" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F57" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -2596,13 +2596,13 @@
         <v>178</v>
       </c>
       <c r="D58" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E58" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F58" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -2616,13 +2616,13 @@
         <v>178</v>
       </c>
       <c r="D59" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E59" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F59" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -2636,13 +2636,13 @@
         <v>178</v>
       </c>
       <c r="D60" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E60" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F60" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -2656,13 +2656,13 @@
         <v>178</v>
       </c>
       <c r="D61" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E61" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F61" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -2676,13 +2676,13 @@
         <v>178</v>
       </c>
       <c r="D62" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E62" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F62" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -2696,13 +2696,13 @@
         <v>178</v>
       </c>
       <c r="D63" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E63" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F63" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -2716,13 +2716,13 @@
         <v>178</v>
       </c>
       <c r="D64" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E64" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F64" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -2736,13 +2736,13 @@
         <v>178</v>
       </c>
       <c r="D65" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E65" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F65" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -2756,13 +2756,13 @@
         <v>178</v>
       </c>
       <c r="D66" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E66" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F66" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -2776,13 +2776,13 @@
         <v>179</v>
       </c>
       <c r="D67" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E67" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F67" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -2796,13 +2796,13 @@
         <v>179</v>
       </c>
       <c r="D68" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E68" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F68" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -2816,13 +2816,13 @@
         <v>178</v>
       </c>
       <c r="D69" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E69" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F69" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -2836,13 +2836,13 @@
         <v>178</v>
       </c>
       <c r="D70" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E70" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F70" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -2856,13 +2856,13 @@
         <v>178</v>
       </c>
       <c r="D71" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E71" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F71" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -2876,13 +2876,13 @@
         <v>179</v>
       </c>
       <c r="D72" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E72" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F72" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -2896,13 +2896,13 @@
         <v>179</v>
       </c>
       <c r="D73" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E73" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F73" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -2916,13 +2916,13 @@
         <v>179</v>
       </c>
       <c r="D74" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E74" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F74" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -2936,13 +2936,13 @@
         <v>178</v>
       </c>
       <c r="D75" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E75" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F75" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -2956,13 +2956,13 @@
         <v>179</v>
       </c>
       <c r="D76" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E76" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F76" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -2976,13 +2976,13 @@
         <v>179</v>
       </c>
       <c r="D77" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E77" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F77" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -2996,13 +2996,13 @@
         <v>179</v>
       </c>
       <c r="D78" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E78" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F78" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -3016,13 +3016,13 @@
         <v>179</v>
       </c>
       <c r="D79" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E79" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F79" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -3036,13 +3036,13 @@
         <v>179</v>
       </c>
       <c r="D80" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E80" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F80" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -3056,13 +3056,13 @@
         <v>179</v>
       </c>
       <c r="D81" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E81" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F81" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -3076,13 +3076,13 @@
         <v>178</v>
       </c>
       <c r="D82" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E82" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F82" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -3096,13 +3096,13 @@
         <v>178</v>
       </c>
       <c r="D83" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E83" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F83" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -3116,13 +3116,13 @@
         <v>178</v>
       </c>
       <c r="D84" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E84" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F84" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -3136,13 +3136,13 @@
         <v>178</v>
       </c>
       <c r="D85" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E85" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F85" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -3156,13 +3156,13 @@
         <v>178</v>
       </c>
       <c r="D86" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E86" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F86" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -3176,13 +3176,13 @@
         <v>178</v>
       </c>
       <c r="D87" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E87" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F87" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -3196,13 +3196,13 @@
         <v>178</v>
       </c>
       <c r="D88" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E88" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F88" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -3216,13 +3216,13 @@
         <v>179</v>
       </c>
       <c r="D89" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E89" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F89" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -3236,13 +3236,13 @@
         <v>179</v>
       </c>
       <c r="D90" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E90" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F90" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -3256,13 +3256,13 @@
         <v>179</v>
       </c>
       <c r="D91" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E91" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F91" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -3276,13 +3276,13 @@
         <v>179</v>
       </c>
       <c r="D92" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E92" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F92" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -3296,13 +3296,13 @@
         <v>179</v>
       </c>
       <c r="D93" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E93" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F93" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -3316,13 +3316,13 @@
         <v>179</v>
       </c>
       <c r="D94" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E94" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F94" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -3336,13 +3336,13 @@
         <v>179</v>
       </c>
       <c r="D95" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E95" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F95" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -3356,13 +3356,13 @@
         <v>179</v>
       </c>
       <c r="D96" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E96" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F96" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -3376,13 +3376,13 @@
         <v>178</v>
       </c>
       <c r="D97" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E97" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F97" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="98" spans="1:6">
@@ -3396,13 +3396,13 @@
         <v>178</v>
       </c>
       <c r="D98" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E98" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F98" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -3416,13 +3416,13 @@
         <v>178</v>
       </c>
       <c r="D99" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E99" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F99" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="100" spans="1:6">
@@ -3436,13 +3436,13 @@
         <v>178</v>
       </c>
       <c r="D100" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E100" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F100" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="101" spans="1:6">
@@ -3456,13 +3456,13 @@
         <v>178</v>
       </c>
       <c r="D101" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E101" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F101" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -3476,13 +3476,13 @@
         <v>178</v>
       </c>
       <c r="D102" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E102" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F102" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="103" spans="1:6">
@@ -3496,13 +3496,13 @@
         <v>178</v>
       </c>
       <c r="D103" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E103" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F103" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="104" spans="1:6">
@@ -3516,13 +3516,13 @@
         <v>178</v>
       </c>
       <c r="D104" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E104" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F104" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -3536,13 +3536,13 @@
         <v>178</v>
       </c>
       <c r="D105" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E105" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F105" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="106" spans="1:6">
@@ -3553,13 +3553,13 @@
         <v>177</v>
       </c>
       <c r="C106" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D106" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E106" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="107" spans="1:6">
@@ -3570,13 +3570,13 @@
         <v>177</v>
       </c>
       <c r="C107" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D107" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E107" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="108" spans="1:6">
@@ -3587,13 +3587,13 @@
         <v>177</v>
       </c>
       <c r="C108" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D108" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E108" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="109" spans="1:6">
@@ -3607,13 +3607,13 @@
         <v>178</v>
       </c>
       <c r="D109" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E109" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F109" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="110" spans="1:6">
@@ -3627,13 +3627,13 @@
         <v>178</v>
       </c>
       <c r="D110" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E110" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F110" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="111" spans="1:6">
@@ -3647,13 +3647,13 @@
         <v>178</v>
       </c>
       <c r="D111" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E111" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F111" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -3667,13 +3667,13 @@
         <v>179</v>
       </c>
       <c r="D112" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E112" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F112" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -3687,13 +3687,13 @@
         <v>179</v>
       </c>
       <c r="D113" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E113" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F113" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -3707,13 +3707,13 @@
         <v>178</v>
       </c>
       <c r="D114" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E114" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F114" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -3727,13 +3727,13 @@
         <v>178</v>
       </c>
       <c r="D115" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E115" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F115" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -3747,13 +3747,13 @@
         <v>178</v>
       </c>
       <c r="D116" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E116" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F116" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -3767,13 +3767,13 @@
         <v>179</v>
       </c>
       <c r="D117" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E117" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F117" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -3787,13 +3787,13 @@
         <v>179</v>
       </c>
       <c r="D118" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E118" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F118" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="119" spans="1:6">
@@ -3807,13 +3807,13 @@
         <v>179</v>
       </c>
       <c r="D119" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E119" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F119" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -3827,13 +3827,13 @@
         <v>179</v>
       </c>
       <c r="D120" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E120" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F120" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -3847,13 +3847,13 @@
         <v>179</v>
       </c>
       <c r="D121" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E121" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F121" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -3867,13 +3867,13 @@
         <v>179</v>
       </c>
       <c r="D122" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E122" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F122" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -3887,13 +3887,13 @@
         <v>178</v>
       </c>
       <c r="D123" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E123" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F123" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -3907,13 +3907,13 @@
         <v>179</v>
       </c>
       <c r="D124" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E124" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F124" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -3927,13 +3927,13 @@
         <v>179</v>
       </c>
       <c r="D125" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E125" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F125" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -3947,13 +3947,13 @@
         <v>179</v>
       </c>
       <c r="D126" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E126" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F126" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -3967,13 +3967,13 @@
         <v>178</v>
       </c>
       <c r="D127" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E127" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F127" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -3987,13 +3987,13 @@
         <v>179</v>
       </c>
       <c r="D128" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E128" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F128" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -4007,13 +4007,13 @@
         <v>179</v>
       </c>
       <c r="D129" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E129" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F129" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -4027,13 +4027,13 @@
         <v>179</v>
       </c>
       <c r="D130" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E130" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F130" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -4047,13 +4047,13 @@
         <v>178</v>
       </c>
       <c r="D131" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E131" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F131" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -4067,13 +4067,13 @@
         <v>179</v>
       </c>
       <c r="D132" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E132" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F132" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -4087,13 +4087,13 @@
         <v>179</v>
       </c>
       <c r="D133" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E133" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F133" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -4107,13 +4107,13 @@
         <v>179</v>
       </c>
       <c r="D134" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E134" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F134" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -4124,13 +4124,13 @@
         <v>177</v>
       </c>
       <c r="C135" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D135" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E135" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -4141,13 +4141,13 @@
         <v>177</v>
       </c>
       <c r="C136" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D136" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E136" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -4161,13 +4161,13 @@
         <v>178</v>
       </c>
       <c r="D137" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E137" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F137" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -4181,13 +4181,13 @@
         <v>178</v>
       </c>
       <c r="D138" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E138" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F138" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -4201,13 +4201,13 @@
         <v>178</v>
       </c>
       <c r="D139" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E139" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F139" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -4221,13 +4221,13 @@
         <v>178</v>
       </c>
       <c r="D140" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E140" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F140" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -4241,13 +4241,13 @@
         <v>178</v>
       </c>
       <c r="D141" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E141" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F141" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -4261,13 +4261,13 @@
         <v>178</v>
       </c>
       <c r="D142" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E142" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F142" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -4281,13 +4281,13 @@
         <v>178</v>
       </c>
       <c r="D143" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E143" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F143" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -4301,13 +4301,13 @@
         <v>178</v>
       </c>
       <c r="D144" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E144" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F144" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -4321,13 +4321,13 @@
         <v>178</v>
       </c>
       <c r="D145" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E145" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F145" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -4341,13 +4341,13 @@
         <v>178</v>
       </c>
       <c r="D146" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E146" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F146" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -4361,13 +4361,13 @@
         <v>179</v>
       </c>
       <c r="D147" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E147" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F147" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -4381,13 +4381,13 @@
         <v>179</v>
       </c>
       <c r="D148" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E148" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F148" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="149" spans="1:6">
@@ -4401,13 +4401,13 @@
         <v>179</v>
       </c>
       <c r="D149" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E149" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F149" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="150" spans="1:6">
@@ -4421,13 +4421,13 @@
         <v>179</v>
       </c>
       <c r="D150" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E150" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F150" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -4441,13 +4441,13 @@
         <v>179</v>
       </c>
       <c r="D151" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E151" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F151" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="152" spans="1:6">
@@ -4461,13 +4461,13 @@
         <v>179</v>
       </c>
       <c r="D152" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E152" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F152" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="153" spans="1:6">
@@ -4481,13 +4481,13 @@
         <v>179</v>
       </c>
       <c r="D153" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E153" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F153" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -4501,13 +4501,13 @@
         <v>179</v>
       </c>
       <c r="D154" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E154" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F154" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -4521,13 +4521,13 @@
         <v>178</v>
       </c>
       <c r="D155" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E155" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F155" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="156" spans="1:6">
@@ -4541,13 +4541,13 @@
         <v>178</v>
       </c>
       <c r="D156" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E156" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F156" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="157" spans="1:6">
@@ -4561,13 +4561,13 @@
         <v>178</v>
       </c>
       <c r="D157" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E157" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F157" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="158" spans="1:6">
@@ -4581,13 +4581,13 @@
         <v>178</v>
       </c>
       <c r="D158" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E158" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F158" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="159" spans="1:6">
@@ -4601,13 +4601,13 @@
         <v>178</v>
       </c>
       <c r="D159" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E159" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F159" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="160" spans="1:6">
@@ -4621,13 +4621,13 @@
         <v>178</v>
       </c>
       <c r="D160" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E160" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F160" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="161" spans="1:6">
@@ -4641,13 +4641,13 @@
         <v>178</v>
       </c>
       <c r="D161" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E161" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F161" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="162" spans="1:6">
@@ -4661,13 +4661,13 @@
         <v>178</v>
       </c>
       <c r="D162" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E162" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F162" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="163" spans="1:6">
@@ -4681,13 +4681,13 @@
         <v>178</v>
       </c>
       <c r="D163" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E163" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F163" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -4701,13 +4701,13 @@
         <v>178</v>
       </c>
       <c r="D164" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E164" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F164" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="165" spans="1:6">
@@ -4721,13 +4721,13 @@
         <v>179</v>
       </c>
       <c r="D165" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E165" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F165" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="166" spans="1:6">
@@ -4741,13 +4741,13 @@
         <v>179</v>
       </c>
       <c r="D166" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E166" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F166" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="167" spans="1:6">
@@ -4761,13 +4761,13 @@
         <v>178</v>
       </c>
       <c r="D167" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E167" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F167" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -4781,13 +4781,13 @@
         <v>178</v>
       </c>
       <c r="D168" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E168" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F168" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="169" spans="1:6">
@@ -4801,13 +4801,13 @@
         <v>178</v>
       </c>
       <c r="D169" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E169" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F169" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
   </sheetData>
